--- a/output/laminas_comunales/comunal_s_isapre_a_2021_biobio.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_biobio.xlsx
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C2">
-        <v>47869</v>
+        <v>24.00909657227347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C3">
-        <v>31989</v>
+        <v>21.7354189842668</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C4">
-        <v>23800</v>
+        <v>17.09710622967694</v>
       </c>
     </row>
     <row r="5">
@@ -429,22 +429,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>19038</v>
+        <v>12.60285579997485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C6">
-        <v>14617</v>
+        <v>11.03082606055831</v>
       </c>
     </row>
     <row r="7">
@@ -459,382 +459,382 @@
         </is>
       </c>
       <c r="C7">
-        <v>8923</v>
+        <v>10.15408075014794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="C8">
-        <v>7209</v>
+        <v>8.491322889836592</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C9">
-        <v>3574</v>
+        <v>7.524922285346769</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C10">
-        <v>3292</v>
+        <v>7.007085817118434</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="C11">
-        <v>2808</v>
+        <v>6.839382544200444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="C12">
-        <v>2011</v>
+        <v>6.29824128572939</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C13">
-        <v>1869</v>
+        <v>6.05747416183514</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C14">
-        <v>1536</v>
+        <v>5.818673883626523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C15">
-        <v>1359</v>
+        <v>5.348106787646135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C16">
-        <v>1180</v>
+        <v>4.997722392138999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="C17">
-        <v>1074</v>
+        <v>4.66739931475855</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="C18">
-        <v>1032</v>
+        <v>4.423380726698262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C19">
-        <v>908</v>
+        <v>4.315009017433705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C20">
-        <v>860</v>
+        <v>4.147576561369664</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="C21">
-        <v>722</v>
+        <v>4.047608434003477</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C22">
-        <v>711</v>
+        <v>3.713118474807081</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C23">
-        <v>646</v>
+        <v>3.594257220307219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="C24">
-        <v>613</v>
+        <v>3.352844234812752</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C25">
-        <v>565</v>
+        <v>3.163638875457623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C26">
-        <v>458</v>
+        <v>3.000331162379954</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="C27">
-        <v>409</v>
+        <v>2.934024963527314</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="C28">
-        <v>250</v>
+        <v>2.834683182467842</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="C29">
-        <v>215</v>
+        <v>2.719657269632406</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C30">
-        <v>196</v>
+        <v>2.596862989508673</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C31">
-        <v>181</v>
+        <v>2.568544292455648</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C32">
-        <v>157</v>
+        <v>2.480790340285401</v>
       </c>
     </row>
     <row r="33">
@@ -849,22 +849,22 @@
         </is>
       </c>
       <c r="C33">
-        <v>144</v>
+        <v>2.105878911962562</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="C34">
-        <v>119</v>
+        <v>1.461144718473709</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
